--- a/DOSSIES_MULTIFORMATO/ANOREG/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/ANOREG/dossie.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1156,9 +1156,638 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Serviços</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Número</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comp.</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Atraso</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Corrigido</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Ações</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>138022</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>12/2022</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8.613,83</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1164 dias</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>138743</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>01/2023</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9.875,84</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1134 dias</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>139423</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>02/2023</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7.517,12</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1102 dias</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>140091</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>03/2023</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.192,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1072 dias</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>140799</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>04/2023</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7.675,20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1044 dias</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>141578</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>05/2023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9.380,80</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1014 dias</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>142347</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>06/2023</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8.315,84</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>980 dias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>143094</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>07/2023</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9.409,92</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>952 dias</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>143867</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>08/2023</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9.376,64</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>920 dias</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>144609</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>09/2023</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6.830,72</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>890 dias</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>145346</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10/2023</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7.770,88</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>857 dias</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ANOREG/AM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Execução de sistemas</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>001/2016</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>146081</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>11/2023</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7.309,12</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>832 dias</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0,00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>